--- a/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_3.xlsx
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
